--- a/01_Accounting_System/جدول_رواتب_وتقييم_30_موظف_الشهري.xlsx
+++ b/01_Accounting_System/جدول_رواتب_وتقييم_30_موظف_الشهري.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45FE2DB-85C4-4175-947B-AC23A3A8F85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1129F215-9FAF-4B6E-AF17-3A53E38674C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="تقييم يومي - الاستقبال" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="100">
   <si>
     <t>📋 شيت التقييم اليومي للـ KPIs — قسم الاستقبال والمكاتب الأمامية</t>
   </si>
@@ -146,268 +146,100 @@
     <t>EMP-101</t>
   </si>
   <si>
-    <t>أحمد محمود علي</t>
-  </si>
-  <si>
-    <t>مشرف استقبال</t>
-  </si>
-  <si>
     <t>EMP-102</t>
   </si>
   <si>
-    <t>محمد حسن إبراهيم</t>
-  </si>
-  <si>
-    <t>موظف استقبال نهار</t>
-  </si>
-  <si>
     <t>EMP-103</t>
   </si>
   <si>
-    <t>عمر خالد فوزي</t>
-  </si>
-  <si>
-    <t>موظف استقبال ليل</t>
-  </si>
-  <si>
     <t>EMP-104</t>
   </si>
   <si>
-    <t>نور الدين طارق</t>
-  </si>
-  <si>
-    <t>موظف استقبال</t>
-  </si>
-  <si>
     <t>EMP-105</t>
   </si>
   <si>
-    <t>مريم عادل القاضي</t>
-  </si>
-  <si>
-    <t>مأمور علاقات نزلاء</t>
-  </si>
-  <si>
     <t>EMP-106</t>
   </si>
   <si>
-    <t>مصطفى كمال الدين</t>
-  </si>
-  <si>
-    <t>مساعد استقبال</t>
-  </si>
-  <si>
     <t>🧹 شيت التقييم اليومي للـ KPIs — قسم الإشراف الداخلي والغرف</t>
   </si>
   <si>
     <t>EMP-107</t>
   </si>
   <si>
-    <t>أميرة عبد العزيز</t>
-  </si>
-  <si>
-    <t>مشرفة الإشراف الداخلي</t>
-  </si>
-  <si>
     <t>EMP-108</t>
   </si>
   <si>
-    <t>سيد مصطفى طه</t>
-  </si>
-  <si>
-    <t>عامل غرف أول</t>
-  </si>
-  <si>
     <t>EMP-109</t>
   </si>
   <si>
-    <t>حسين علي كمال</t>
-  </si>
-  <si>
-    <t>عامل تنظيف غرف</t>
-  </si>
-  <si>
     <t>EMP-110</t>
   </si>
   <si>
-    <t>إبراهيم خليفة</t>
-  </si>
-  <si>
     <t>EMP-111</t>
   </si>
   <si>
-    <t>رمضان فتحي</t>
-  </si>
-  <si>
     <t>EMP-112</t>
   </si>
   <si>
-    <t>عاطف منصور</t>
-  </si>
-  <si>
     <t>EMP-113</t>
   </si>
   <si>
-    <t>حسن شحاتة</t>
-  </si>
-  <si>
-    <t>عامل غسيل وكتانيات</t>
-  </si>
-  <si>
     <t>EMP-114</t>
   </si>
   <si>
-    <t>زينب أحمد السيد</t>
-  </si>
-  <si>
-    <t>عامله نظافة أماكن عامة</t>
-  </si>
-  <si>
     <t>EMP-115</t>
   </si>
   <si>
-    <t>فاطمة محمود</t>
-  </si>
-  <si>
     <t>EMP-116</t>
   </si>
   <si>
-    <t>محمود جابر</t>
-  </si>
-  <si>
-    <t>عامل نظافة ممرات</t>
-  </si>
-  <si>
     <t>EMP-117</t>
   </si>
   <si>
-    <t>علي عبد السميع</t>
-  </si>
-  <si>
-    <t>مساعد إشراف داخلي</t>
-  </si>
-  <si>
     <t>EMP-118</t>
   </si>
   <si>
-    <t>فتحي رجب</t>
-  </si>
-  <si>
-    <t>عامل نظافة وأماكن عامة</t>
-  </si>
-  <si>
     <t>🍽️ شيت التقييم اليومي للـ KPIs — قسم المطعم والكافيه</t>
   </si>
   <si>
     <t>EMP-119</t>
   </si>
   <si>
-    <t>خالد رجب سلامة</t>
-  </si>
-  <si>
-    <t>مدير مطعم وكافيه</t>
-  </si>
-  <si>
     <t>EMP-120</t>
   </si>
   <si>
-    <t>طارق صلاح الدين</t>
-  </si>
-  <si>
-    <t>مشرف أغذية ومشروبات</t>
-  </si>
-  <si>
     <t>EMP-121</t>
   </si>
   <si>
-    <t>إسلام يوسف أحمد</t>
-  </si>
-  <si>
-    <t>ويتر كافيه رئيسي</t>
-  </si>
-  <si>
     <t>EMP-122</t>
   </si>
   <si>
-    <t>مصطفى ربيع جابر</t>
-  </si>
-  <si>
-    <t>ويتر كافيه</t>
-  </si>
-  <si>
     <t>EMP-123</t>
   </si>
   <si>
-    <t>وليد صبري</t>
-  </si>
-  <si>
-    <t>ويتر مطعم إفطار</t>
-  </si>
-  <si>
     <t>EMP-124</t>
   </si>
   <si>
-    <t>كريم شعبان</t>
-  </si>
-  <si>
-    <t>باريستا بائع كافيه</t>
-  </si>
-  <si>
     <t>EMP-125</t>
   </si>
   <si>
-    <t>سامح فاروق</t>
-  </si>
-  <si>
-    <t>مساعد ويتر تجهيز</t>
-  </si>
-  <si>
     <t>EMP-126</t>
   </si>
   <si>
-    <t>أحمد بدوي</t>
-  </si>
-  <si>
-    <t>عامل غسيل أطباق وتجهيز</t>
-  </si>
-  <si>
     <t>🔧 شيت التقييم اليومي للـ KPIs — قسم الصيانة والخدمات المعاونة</t>
   </si>
   <si>
     <t>EMP-127</t>
   </si>
   <si>
-    <t>المهندس تامر فؤاد</t>
-  </si>
-  <si>
-    <t>مشرف صيانة الفندق</t>
-  </si>
-  <si>
     <t>EMP-128</t>
   </si>
   <si>
-    <t>جمال عبد المعطي</t>
-  </si>
-  <si>
-    <t>فني كهرباء وسباكة</t>
-  </si>
-  <si>
     <t>EMP-129</t>
   </si>
   <si>
-    <t>رفعت عبد الصمد</t>
-  </si>
-  <si>
-    <t>سائق ومسؤول خدمات</t>
-  </si>
-  <si>
     <t>EMP-130</t>
-  </si>
-  <si>
-    <t>صبحي عبد العال</t>
-  </si>
-  <si>
-    <t>مسؤول أمن وحراسة</t>
   </si>
   <si>
     <t>🏨 فندق هينو الأهرامات — كشف الرواتب المالي الشهري المرتبط آلياً بتقييم الـ KPIs اليومي</t>
@@ -1301,12 +1133,8 @@
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1348,14 +1176,10 @@
     </row>
     <row r="5" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -1397,14 +1221,10 @@
     </row>
     <row r="6" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1446,14 +1266,10 @@
     </row>
     <row r="7" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>47</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1495,14 +1311,10 @@
     </row>
     <row r="8" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1544,14 +1356,10 @@
     </row>
     <row r="9" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>53</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -1615,7 +1423,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1762,14 +1570,10 @@
     </row>
     <row r="4" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1811,14 +1615,10 @@
     </row>
     <row r="5" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>60</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -1860,14 +1660,10 @@
     </row>
     <row r="6" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>63</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1909,14 +1705,10 @@
     </row>
     <row r="7" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>63</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1958,14 +1750,10 @@
     </row>
     <row r="8" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2007,14 +1795,10 @@
     </row>
     <row r="9" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>63</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
@@ -2056,14 +1840,10 @@
     </row>
     <row r="10" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>72</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -2105,14 +1885,10 @@
     </row>
     <row r="11" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -2154,14 +1930,10 @@
     </row>
     <row r="12" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2203,14 +1975,10 @@
     </row>
     <row r="13" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>80</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2252,14 +2020,10 @@
     </row>
     <row r="14" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2301,14 +2065,10 @@
     </row>
     <row r="15" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2372,7 +2132,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -2519,874 +2279,362 @@
     </row>
     <row r="4" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>5</v>
-      </c>
-      <c r="F4" s="3">
-        <v>5</v>
-      </c>
-      <c r="G4" s="3">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3">
-        <v>5</v>
-      </c>
-      <c r="K4" s="3">
-        <v>5</v>
-      </c>
-      <c r="L4" s="3">
-        <v>5</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5</v>
-      </c>
-      <c r="N4" s="3">
-        <v>5</v>
-      </c>
-      <c r="O4" s="3">
-        <v>5</v>
-      </c>
-      <c r="P4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>5</v>
-      </c>
-      <c r="R4" s="3">
-        <v>5</v>
-      </c>
-      <c r="S4" s="3">
-        <v>5</v>
-      </c>
-      <c r="T4" s="3">
-        <v>5</v>
-      </c>
-      <c r="U4" s="3">
-        <v>5</v>
-      </c>
-      <c r="V4" s="3">
-        <v>5</v>
-      </c>
-      <c r="W4" s="3">
-        <v>5</v>
-      </c>
-      <c r="X4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>5</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
       <c r="AH4" s="4">
         <f t="shared" ref="AH4:AH11" si="0">SUM(D4:AG4)</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" ref="AI4:AI11" si="1">ROUND((AH4/150)*100, 0)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="7">
-        <v>5</v>
-      </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7">
-        <v>5</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5</v>
-      </c>
-      <c r="H5" s="8">
-        <v>4</v>
-      </c>
-      <c r="I5" s="7">
-        <v>5</v>
-      </c>
-      <c r="J5" s="7">
-        <v>5</v>
-      </c>
-      <c r="K5" s="7">
-        <v>5</v>
-      </c>
-      <c r="L5" s="7">
-        <v>5</v>
-      </c>
-      <c r="M5" s="8">
-        <v>4</v>
-      </c>
-      <c r="N5" s="7">
-        <v>5</v>
-      </c>
-      <c r="O5" s="7">
-        <v>5</v>
-      </c>
-      <c r="P5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>5</v>
-      </c>
-      <c r="R5" s="8">
-        <v>4</v>
-      </c>
-      <c r="S5" s="7">
-        <v>5</v>
-      </c>
-      <c r="T5" s="7">
-        <v>5</v>
-      </c>
-      <c r="U5" s="7">
-        <v>5</v>
-      </c>
-      <c r="V5" s="7">
-        <v>5</v>
-      </c>
-      <c r="W5" s="8">
-        <v>4</v>
-      </c>
-      <c r="X5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB5" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AF5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG5" s="8">
-        <v>4</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="8"/>
       <c r="AH5" s="8">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="5">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3">
-        <v>5</v>
-      </c>
-      <c r="I6" s="3">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3">
-        <v>5</v>
-      </c>
-      <c r="L6" s="3">
-        <v>5</v>
-      </c>
-      <c r="M6" s="3">
-        <v>5</v>
-      </c>
-      <c r="N6" s="3">
-        <v>5</v>
-      </c>
-      <c r="O6" s="3">
-        <v>5</v>
-      </c>
-      <c r="P6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>5</v>
-      </c>
-      <c r="R6" s="3">
-        <v>5</v>
-      </c>
-      <c r="S6" s="3">
-        <v>5</v>
-      </c>
-      <c r="T6" s="3">
-        <v>5</v>
-      </c>
-      <c r="U6" s="3">
-        <v>5</v>
-      </c>
-      <c r="V6" s="3">
-        <v>5</v>
-      </c>
-      <c r="W6" s="3">
-        <v>5</v>
-      </c>
-      <c r="X6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>5</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
       <c r="AH6" s="4">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4</v>
-      </c>
-      <c r="I7" s="7">
-        <v>5</v>
-      </c>
-      <c r="J7" s="8">
-        <v>3</v>
-      </c>
-      <c r="K7" s="7">
-        <v>5</v>
-      </c>
-      <c r="L7" s="7">
-        <v>5</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>5</v>
-      </c>
-      <c r="O7" s="7">
-        <v>5</v>
-      </c>
-      <c r="P7" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>3</v>
-      </c>
-      <c r="R7" s="8">
-        <v>4</v>
-      </c>
-      <c r="S7" s="7">
-        <v>5</v>
-      </c>
-      <c r="T7" s="7">
-        <v>5</v>
-      </c>
-      <c r="U7" s="7">
-        <v>5</v>
-      </c>
-      <c r="V7" s="7">
-        <v>5</v>
-      </c>
-      <c r="W7" s="9">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB7" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE7" s="8">
-        <v>3</v>
-      </c>
-      <c r="AF7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG7" s="8">
-        <v>4</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="8"/>
       <c r="AH7" s="8">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="5">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="3">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3">
-        <v>5</v>
-      </c>
-      <c r="L8" s="3">
-        <v>5</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5</v>
-      </c>
-      <c r="N8" s="3">
-        <v>5</v>
-      </c>
-      <c r="O8" s="3">
-        <v>5</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5</v>
-      </c>
-      <c r="R8" s="3">
-        <v>5</v>
-      </c>
-      <c r="S8" s="3">
-        <v>5</v>
-      </c>
-      <c r="T8" s="3">
-        <v>5</v>
-      </c>
-      <c r="U8" s="3">
-        <v>5</v>
-      </c>
-      <c r="V8" s="3">
-        <v>5</v>
-      </c>
-      <c r="W8" s="3">
-        <v>5</v>
-      </c>
-      <c r="X8" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>5</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
       <c r="AH8" s="4">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="5">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="7">
-        <v>5</v>
-      </c>
-      <c r="E9" s="7">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>5</v>
-      </c>
-      <c r="G9" s="7">
-        <v>5</v>
-      </c>
-      <c r="H9" s="8">
-        <v>4</v>
-      </c>
-      <c r="I9" s="7">
-        <v>5</v>
-      </c>
-      <c r="J9" s="7">
-        <v>5</v>
-      </c>
-      <c r="K9" s="7">
-        <v>5</v>
-      </c>
-      <c r="L9" s="7">
-        <v>5</v>
-      </c>
-      <c r="M9" s="8">
-        <v>4</v>
-      </c>
-      <c r="N9" s="7">
-        <v>5</v>
-      </c>
-      <c r="O9" s="7">
-        <v>5</v>
-      </c>
-      <c r="P9" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>5</v>
-      </c>
-      <c r="R9" s="8">
-        <v>4</v>
-      </c>
-      <c r="S9" s="7">
-        <v>5</v>
-      </c>
-      <c r="T9" s="7">
-        <v>5</v>
-      </c>
-      <c r="U9" s="7">
-        <v>5</v>
-      </c>
-      <c r="V9" s="7">
-        <v>5</v>
-      </c>
-      <c r="W9" s="8">
-        <v>4</v>
-      </c>
-      <c r="X9" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="8">
-        <v>4</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="8"/>
       <c r="AH9" s="8">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="5">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="3">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
-        <v>5</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>5</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
       <c r="AH10" s="4">
         <f t="shared" si="0"/>
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="5">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="7">
-        <v>5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>5</v>
-      </c>
-      <c r="F11" s="7">
-        <v>5</v>
-      </c>
-      <c r="G11" s="7">
-        <v>5</v>
-      </c>
-      <c r="H11" s="8">
-        <v>4</v>
-      </c>
-      <c r="I11" s="7">
-        <v>5</v>
-      </c>
-      <c r="J11" s="7">
-        <v>5</v>
-      </c>
-      <c r="K11" s="7">
-        <v>5</v>
-      </c>
-      <c r="L11" s="7">
-        <v>5</v>
-      </c>
-      <c r="M11" s="8">
-        <v>4</v>
-      </c>
-      <c r="N11" s="7">
-        <v>5</v>
-      </c>
-      <c r="O11" s="7">
-        <v>5</v>
-      </c>
-      <c r="P11" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>5</v>
-      </c>
-      <c r="R11" s="8">
-        <v>4</v>
-      </c>
-      <c r="S11" s="7">
-        <v>5</v>
-      </c>
-      <c r="T11" s="7">
-        <v>5</v>
-      </c>
-      <c r="U11" s="7">
-        <v>5</v>
-      </c>
-      <c r="V11" s="7">
-        <v>5</v>
-      </c>
-      <c r="W11" s="8">
-        <v>4</v>
-      </c>
-      <c r="X11" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y11" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB11" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AF11" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG11" s="8">
-        <v>4</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="8"/>
       <c r="AH11" s="8">
         <f t="shared" si="0"/>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="5">
         <f t="shared" si="1"/>
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3413,7 +2661,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -3560,438 +2808,182 @@
     </row>
     <row r="4" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>5</v>
-      </c>
-      <c r="F4" s="3">
-        <v>5</v>
-      </c>
-      <c r="G4" s="3">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3">
-        <v>5</v>
-      </c>
-      <c r="K4" s="3">
-        <v>5</v>
-      </c>
-      <c r="L4" s="3">
-        <v>5</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5</v>
-      </c>
-      <c r="N4" s="3">
-        <v>5</v>
-      </c>
-      <c r="O4" s="3">
-        <v>5</v>
-      </c>
-      <c r="P4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>5</v>
-      </c>
-      <c r="R4" s="3">
-        <v>5</v>
-      </c>
-      <c r="S4" s="3">
-        <v>5</v>
-      </c>
-      <c r="T4" s="3">
-        <v>5</v>
-      </c>
-      <c r="U4" s="3">
-        <v>5</v>
-      </c>
-      <c r="V4" s="3">
-        <v>5</v>
-      </c>
-      <c r="W4" s="3">
-        <v>5</v>
-      </c>
-      <c r="X4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>5</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
       <c r="AH4" s="4">
         <f>SUM(D4:AG4)</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="5">
         <f>ROUND((AH4/150)*100, 0)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="7">
-        <v>5</v>
-      </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7">
-        <v>5</v>
-      </c>
-      <c r="G5" s="7">
-        <v>5</v>
-      </c>
-      <c r="H5" s="8">
-        <v>4</v>
-      </c>
-      <c r="I5" s="7">
-        <v>5</v>
-      </c>
-      <c r="J5" s="7">
-        <v>5</v>
-      </c>
-      <c r="K5" s="7">
-        <v>5</v>
-      </c>
-      <c r="L5" s="7">
-        <v>5</v>
-      </c>
-      <c r="M5" s="8">
-        <v>4</v>
-      </c>
-      <c r="N5" s="7">
-        <v>5</v>
-      </c>
-      <c r="O5" s="7">
-        <v>5</v>
-      </c>
-      <c r="P5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>5</v>
-      </c>
-      <c r="R5" s="8">
-        <v>4</v>
-      </c>
-      <c r="S5" s="7">
-        <v>5</v>
-      </c>
-      <c r="T5" s="7">
-        <v>5</v>
-      </c>
-      <c r="U5" s="7">
-        <v>5</v>
-      </c>
-      <c r="V5" s="7">
-        <v>5</v>
-      </c>
-      <c r="W5" s="8">
-        <v>4</v>
-      </c>
-      <c r="X5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB5" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AF5" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG5" s="8">
-        <v>4</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="8"/>
       <c r="AH5" s="8">
         <f>SUM(D5:AG5)</f>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="5">
         <f>ROUND((AH5/150)*100, 0)</f>
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>5</v>
-      </c>
-      <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3">
-        <v>5</v>
-      </c>
-      <c r="I6" s="3">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3">
-        <v>5</v>
-      </c>
-      <c r="L6" s="3">
-        <v>5</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
-        <v>5</v>
-      </c>
-      <c r="O6" s="3">
-        <v>5</v>
-      </c>
-      <c r="P6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>5</v>
-      </c>
-      <c r="R6" s="3">
-        <v>5</v>
-      </c>
-      <c r="S6" s="3">
-        <v>5</v>
-      </c>
-      <c r="T6" s="3">
-        <v>5</v>
-      </c>
-      <c r="U6" s="3">
-        <v>5</v>
-      </c>
-      <c r="V6" s="3">
-        <v>5</v>
-      </c>
-      <c r="W6" s="3">
-        <v>5</v>
-      </c>
-      <c r="X6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>5</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
       <c r="AH6" s="4">
         <f>SUM(D6:AG6)</f>
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="5">
         <f>ROUND((AH6/150)*100, 0)</f>
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="7">
-        <v>5</v>
-      </c>
-      <c r="E7" s="7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="8">
-        <v>4</v>
-      </c>
-      <c r="I7" s="7">
-        <v>5</v>
-      </c>
-      <c r="J7" s="7">
-        <v>5</v>
-      </c>
-      <c r="K7" s="7">
-        <v>5</v>
-      </c>
-      <c r="L7" s="7">
-        <v>5</v>
-      </c>
-      <c r="M7" s="8">
-        <v>4</v>
-      </c>
-      <c r="N7" s="7">
-        <v>5</v>
-      </c>
-      <c r="O7" s="7">
-        <v>5</v>
-      </c>
-      <c r="P7" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>5</v>
-      </c>
-      <c r="R7" s="8">
-        <v>4</v>
-      </c>
-      <c r="S7" s="7">
-        <v>5</v>
-      </c>
-      <c r="T7" s="7">
-        <v>5</v>
-      </c>
-      <c r="U7" s="7">
-        <v>5</v>
-      </c>
-      <c r="V7" s="7">
-        <v>5</v>
-      </c>
-      <c r="W7" s="8">
-        <v>4</v>
-      </c>
-      <c r="X7" s="7">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="7">
-        <v>5</v>
-      </c>
-      <c r="Z7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AA7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AB7" s="8">
-        <v>4</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AD7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AE7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AF7" s="7">
-        <v>5</v>
-      </c>
-      <c r="AG7" s="8">
-        <v>4</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="8"/>
       <c r="AH7" s="8">
         <f>SUM(D7:AG7)</f>
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="5">
         <f>ROUND((AH7/150)*100, 0)</f>
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4025,7 +3017,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -4052,49 +3044,49 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
@@ -4131,31 +3123,27 @@
         <f t="shared" ref="K4:K33" si="4">ROUND((E4/30)*J4, 2)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="15">
-        <v>0</v>
-      </c>
+      <c r="L4" s="15"/>
       <c r="M4" s="12">
         <f t="shared" ref="M4:M33" si="5">ROUND((E4/30)*L4, 2)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="12">
-        <v>500</v>
-      </c>
+      <c r="N4" s="12"/>
       <c r="O4" s="12">
         <f t="shared" ref="O4:O33" si="6">K4+M4+N4</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P4" s="16">
         <f t="shared" ref="P4:P33" si="7">E4+I4-O4</f>
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -4187,16 +3175,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L5" s="20">
-        <v>0</v>
-      </c>
+      <c r="L5" s="20"/>
       <c r="M5" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N5" s="18">
-        <v>0</v>
-      </c>
+      <c r="N5" s="18"/>
       <c r="O5" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4206,12 +3190,12 @@
         <v>0</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -4243,31 +3227,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L6" s="15">
-        <v>0</v>
-      </c>
+      <c r="L6" s="15"/>
       <c r="M6" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N6" s="12">
-        <v>300</v>
-      </c>
+      <c r="N6" s="12"/>
       <c r="O6" s="12">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P6" s="16">
         <f t="shared" si="7"/>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -4299,16 +3279,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L7" s="20">
-        <v>1</v>
-      </c>
+      <c r="L7" s="20"/>
       <c r="M7" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
+      <c r="N7" s="18"/>
       <c r="O7" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4318,12 +3294,12 @@
         <v>0</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -4355,31 +3331,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L8" s="15">
-        <v>0</v>
-      </c>
+      <c r="L8" s="15"/>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N8" s="12">
-        <v>200</v>
-      </c>
+      <c r="N8" s="12"/>
       <c r="O8" s="12">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P8" s="16">
         <f t="shared" si="7"/>
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -4411,31 +3383,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="20">
-        <v>0</v>
-      </c>
+      <c r="L9" s="20"/>
       <c r="M9" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N9" s="18">
-        <v>150</v>
-      </c>
+      <c r="N9" s="18"/>
       <c r="O9" s="18">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P9" s="16">
         <f t="shared" si="7"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -4467,31 +3435,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L10" s="15">
-        <v>0</v>
-      </c>
+      <c r="L10" s="15"/>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N10" s="12">
-        <v>400</v>
-      </c>
+      <c r="N10" s="12"/>
       <c r="O10" s="12">
         <f t="shared" si="6"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P10" s="16">
         <f t="shared" si="7"/>
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -4523,31 +3487,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L11" s="20">
-        <v>0</v>
-      </c>
+      <c r="L11" s="20"/>
       <c r="M11" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="18">
-        <v>200</v>
-      </c>
+      <c r="N11" s="18"/>
       <c r="O11" s="18">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P11" s="16">
         <f t="shared" si="7"/>
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4579,16 +3539,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L12" s="15">
-        <v>1</v>
-      </c>
+      <c r="L12" s="15"/>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N12" s="12">
-        <v>0</v>
-      </c>
+      <c r="N12" s="12"/>
       <c r="O12" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4598,12 +3554,12 @@
         <v>0</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -4635,31 +3591,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
+      <c r="L13" s="20"/>
       <c r="M13" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N13" s="18">
-        <v>100</v>
-      </c>
+      <c r="N13" s="18"/>
       <c r="O13" s="18">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P13" s="16">
         <f t="shared" si="7"/>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4691,16 +3643,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
+      <c r="L14" s="15"/>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N14" s="12">
-        <v>0</v>
-      </c>
+      <c r="N14" s="12"/>
       <c r="O14" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4710,12 +3658,12 @@
         <v>0</v>
       </c>
       <c r="Q14" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="17" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
@@ -4747,31 +3695,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L15" s="20">
-        <v>2</v>
-      </c>
+      <c r="L15" s="20"/>
       <c r="M15" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="18">
-        <v>300</v>
-      </c>
+      <c r="N15" s="18"/>
       <c r="O15" s="18">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P15" s="16">
         <f t="shared" si="7"/>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4803,31 +3747,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
+      <c r="L16" s="15"/>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N16" s="12">
-        <v>250</v>
-      </c>
+      <c r="N16" s="12"/>
       <c r="O16" s="12">
         <f t="shared" si="6"/>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="P16" s="16">
         <f t="shared" si="7"/>
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -4859,16 +3799,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
+      <c r="L17" s="20"/>
       <c r="M17" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="18">
-        <v>0</v>
-      </c>
+      <c r="N17" s="18"/>
       <c r="O17" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4878,12 +3814,12 @@
         <v>0</v>
       </c>
       <c r="Q17" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4915,31 +3851,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L18" s="15">
-        <v>0</v>
-      </c>
+      <c r="L18" s="15"/>
       <c r="M18" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="12">
-        <v>100</v>
-      </c>
+      <c r="N18" s="12"/>
       <c r="O18" s="12">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P18" s="16">
         <f t="shared" si="7"/>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -4971,16 +3903,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
+      <c r="L19" s="20"/>
       <c r="M19" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N19" s="18">
-        <v>0</v>
-      </c>
+      <c r="N19" s="18"/>
       <c r="O19" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4990,12 +3918,12 @@
         <v>0</v>
       </c>
       <c r="Q19" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5027,31 +3955,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L20" s="15">
-        <v>0</v>
-      </c>
+      <c r="L20" s="15"/>
       <c r="M20" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N20" s="12">
-        <v>150</v>
-      </c>
+      <c r="N20" s="12"/>
       <c r="O20" s="12">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P20" s="16">
         <f t="shared" si="7"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -5083,16 +4007,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L21" s="20">
-        <v>1</v>
-      </c>
+      <c r="L21" s="20"/>
       <c r="M21" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N21" s="18">
-        <v>0</v>
-      </c>
+      <c r="N21" s="18"/>
       <c r="O21" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -5102,12 +4022,12 @@
         <v>0</v>
       </c>
       <c r="Q21" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5122,11 +4042,11 @@
       </c>
       <c r="G22" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI4</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="12">
         <f t="shared" si="3"/>
@@ -5139,31 +4059,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L22" s="15">
-        <v>0</v>
-      </c>
+      <c r="L22" s="15"/>
       <c r="M22" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N22" s="12">
-        <v>1000</v>
-      </c>
+      <c r="N22" s="12"/>
       <c r="O22" s="12">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P22" s="16">
         <f t="shared" si="7"/>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -5178,11 +4094,11 @@
       </c>
       <c r="G23" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI5</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H23" s="19">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="18">
         <f t="shared" si="3"/>
@@ -5195,31 +4111,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L23" s="20">
-        <v>0</v>
-      </c>
+      <c r="L23" s="20"/>
       <c r="M23" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N23" s="18">
-        <v>300</v>
-      </c>
+      <c r="N23" s="18"/>
       <c r="O23" s="18">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P23" s="16">
         <f t="shared" si="7"/>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -5234,11 +4146,11 @@
       </c>
       <c r="G24" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI6</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="12">
         <f t="shared" si="3"/>
@@ -5251,16 +4163,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L24" s="15">
-        <v>0</v>
-      </c>
+      <c r="L24" s="15"/>
       <c r="M24" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N24" s="12">
-        <v>0</v>
-      </c>
+      <c r="N24" s="12"/>
       <c r="O24" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -5270,12 +4178,12 @@
         <v>0</v>
       </c>
       <c r="Q24" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -5290,11 +4198,11 @@
       </c>
       <c r="G25" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI7</f>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H25" s="19">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="I25" s="18">
         <f t="shared" si="3"/>
@@ -5307,31 +4215,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L25" s="20">
-        <v>1</v>
-      </c>
+      <c r="L25" s="20"/>
       <c r="M25" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N25" s="18">
-        <v>200</v>
-      </c>
+      <c r="N25" s="18"/>
       <c r="O25" s="18">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P25" s="16">
         <f t="shared" si="7"/>
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5346,11 +4250,11 @@
       </c>
       <c r="G26" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI8</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="12">
         <f t="shared" si="3"/>
@@ -5363,31 +4267,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L26" s="15">
-        <v>0</v>
-      </c>
+      <c r="L26" s="15"/>
       <c r="M26" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N26" s="12">
-        <v>150</v>
-      </c>
+      <c r="N26" s="12"/>
       <c r="O26" s="12">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P26" s="16">
         <f t="shared" si="7"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -5402,11 +4302,11 @@
       </c>
       <c r="G27" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI9</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H27" s="19">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="18">
         <f t="shared" si="3"/>
@@ -5419,31 +4319,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
+      <c r="L27" s="20"/>
       <c r="M27" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N27" s="18">
-        <v>400</v>
-      </c>
+      <c r="N27" s="18"/>
       <c r="O27" s="18">
         <f t="shared" si="6"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P27" s="16">
         <f t="shared" si="7"/>
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -5458,11 +4354,11 @@
       </c>
       <c r="G28" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI10</f>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H28" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="12">
         <f t="shared" si="3"/>
@@ -5475,16 +4371,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L28" s="15">
-        <v>0</v>
-      </c>
+      <c r="L28" s="15"/>
       <c r="M28" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N28" s="12">
-        <v>0</v>
-      </c>
+      <c r="N28" s="12"/>
       <c r="O28" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -5494,12 +4386,12 @@
         <v>0</v>
       </c>
       <c r="Q28" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
@@ -5514,11 +4406,11 @@
       </c>
       <c r="G29" s="13">
         <f>'تقييم يومي - المطعم والخدمة'!AI11</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="18">
         <f t="shared" si="3"/>
@@ -5531,31 +4423,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L29" s="20">
-        <v>0</v>
-      </c>
+      <c r="L29" s="20"/>
       <c r="M29" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N29" s="18">
-        <v>100</v>
-      </c>
+      <c r="N29" s="18"/>
       <c r="O29" s="18">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P29" s="16">
         <f t="shared" si="7"/>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -5570,11 +4458,11 @@
       </c>
       <c r="G30" s="13">
         <f>'تقييم يومي - الصيانة والخدمات'!AI4</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H30" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12">
         <f t="shared" si="3"/>
@@ -5587,31 +4475,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
+      <c r="L30" s="15"/>
       <c r="M30" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N30" s="12">
-        <v>600</v>
-      </c>
+      <c r="N30" s="12"/>
       <c r="O30" s="12">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P30" s="16">
         <f t="shared" si="7"/>
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -5626,11 +4510,11 @@
       </c>
       <c r="G31" s="13">
         <f>'تقييم يومي - الصيانة والخدمات'!AI5</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H31" s="19">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="18">
         <f t="shared" si="3"/>
@@ -5643,31 +4527,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L31" s="20">
-        <v>0</v>
-      </c>
+      <c r="L31" s="20"/>
       <c r="M31" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N31" s="18">
-        <v>200</v>
-      </c>
+      <c r="N31" s="18"/>
       <c r="O31" s="18">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P31" s="16">
         <f t="shared" si="7"/>
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -5682,11 +4562,11 @@
       </c>
       <c r="G32" s="13">
         <f>'تقييم يومي - الصيانة والخدمات'!AI6</f>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H32" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="12">
         <f t="shared" si="3"/>
@@ -5699,31 +4579,27 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L32" s="15">
-        <v>0</v>
-      </c>
+      <c r="L32" s="15"/>
       <c r="M32" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N32" s="12">
-        <v>150</v>
-      </c>
+      <c r="N32" s="12"/>
       <c r="O32" s="12">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P32" s="16">
         <f t="shared" si="7"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="15" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -5738,11 +4614,11 @@
       </c>
       <c r="G33" s="13">
         <f>'تقييم يومي - الصيانة والخدمات'!AI7</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H33" s="19">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="18">
         <f t="shared" si="3"/>
@@ -5755,16 +4631,12 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
+      <c r="L33" s="20"/>
       <c r="M33" s="18">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N33" s="18">
-        <v>0</v>
-      </c>
+      <c r="N33" s="18"/>
       <c r="O33" s="18">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -5774,18 +4646,18 @@
         <v>0</v>
       </c>
       <c r="Q33" s="20" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="D34" s="22">
         <f>SUM(D4:D33)</f>
@@ -5801,10 +4673,10 @@
       </c>
       <c r="G34" s="21">
         <f>AVERAGE(G4:G33)</f>
-        <v>38.633333333333333</v>
+        <v>0</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="I34" s="22">
         <f t="shared" ref="I34:P34" si="8">SUM(I4:I33)</f>
@@ -5820,7 +4692,7 @@
       </c>
       <c r="L34" s="21">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M34" s="22">
         <f t="shared" si="8"/>
@@ -5828,18 +4700,18 @@
       </c>
       <c r="N34" s="22">
         <f t="shared" si="8"/>
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="O34" s="22">
         <f t="shared" si="8"/>
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="P34" s="22">
         <f t="shared" si="8"/>
-        <v>-5750</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="21" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -5862,7 +4734,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -5871,42 +4743,42 @@
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="23" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
